--- a/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_standardized_matrix.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_standardized_matrix.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,1101 +463,925 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>004ABC</t>
+          <t>DR-03</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.2411460175584779</v>
+        <v>-0.1751863912993838</v>
       </c>
       <c r="C2" t="n">
-        <v>0.892753573171803</v>
+        <v>1.219156454623142</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.891102364811515</v>
+        <v>-2.401862901748136</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.9381621166049322</v>
+        <v>-1.057489420970179</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.651806256861148</v>
+        <v>-0.7445205836245899</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>010B</t>
+          <t>DR-10</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.1941855598920198</v>
+        <v>0.8476290762913705</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.5351761673229167</v>
+        <v>-0.2737943453064912</v>
       </c>
       <c r="D3" t="n">
-        <v>1.009388676960088</v>
+        <v>0.9381680679730683</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3413891383782838</v>
+        <v>0.451200284001553</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.04494662250532432</v>
+        <v>-0.5432567630517888</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>011A</t>
+          <t>DR-54</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6980631357706848</v>
+        <v>0.949910623050446</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.6318589101689126</v>
+        <v>-0.4995576370031679</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9826970416063621</v>
+        <v>0.958849374287131</v>
       </c>
       <c r="E4" t="n">
-        <v>0.639778672844596</v>
+        <v>-0.4124832255437746</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08576160643285323</v>
+        <v>-0.6196860620034853</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>016C</t>
+          <t>DR-163</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.7577110518895174</v>
+        <v>1.819303770502587</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.383009450741656</v>
+        <v>1.146329586333892</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.04048231361981729</v>
+        <v>-2.970598825384873</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4622894919690663</v>
+        <v>-0.08171081763279836</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.567779538258034</v>
+        <v>-0.5891143424228067</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>026C</t>
+          <t>DR-164</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.543351373766931</v>
+        <v>2.739837691334266</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.873860299036716</v>
+        <v>0.1850149249157858</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.031585101835242</v>
+        <v>-1.802105018640304</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.333848547820427</v>
+        <v>-0.533170455457239</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2958284029406383</v>
+        <v>-0.4821133238904314</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>030ABC</t>
+          <t>DR-167</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.435600069429636</v>
+        <v>1.819303770502587</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.1633194640690834</v>
+        <v>-1.7303317110915</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.375064081306138</v>
+        <v>-0.5250343537469027</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3897761366128767</v>
+        <v>-0.2636356419838351</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3098328560411574</v>
+        <v>-0.5738284826324674</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>033ABC</t>
+          <t>DR-168</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.590311831433389</v>
+        <v>2.63755614457519</v>
       </c>
       <c r="C8" t="n">
-        <v>-2.119285723184246</v>
+        <v>-1.511851106223749</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2762584259110678</v>
+        <v>-0.5560563132179968</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1078692773330733</v>
+        <v>-3.389434896742562</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.02627401837129895</v>
+        <v>3.935500155517633</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>035C</t>
+          <t>DR-175</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.623441900095469</v>
+        <v>0.4896436626346066</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.494566461717806</v>
+        <v>-1.191412885751047</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3385389084030963</v>
+        <v>-0.4423091284906499</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.377147331966017</v>
+        <v>1.075992610055619</v>
       </c>
       <c r="F9" t="n">
-        <v>2.34514670664992</v>
+        <v>3.204326528879736</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>036C</t>
+          <t>DR-195</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.05991640809797</v>
+        <v>-0.7888756718538364</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.44250652326227</v>
+        <v>1.335679443885943</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3207444848339441</v>
+        <v>1.196684396898858</v>
       </c>
       <c r="E10" t="n">
-        <v>0.891495289290515</v>
+        <v>0.7324981864557588</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6552760325206264</v>
+        <v>-0.02353753018025173</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>DR-197</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.261588627768183</v>
+        <v>1.001051396429983</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1044173622736761</v>
+        <v>0.3161032878364363</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.54855971110536</v>
+        <v>0.338410184865236</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5856139463769443</v>
+        <v>0.2697348657726139</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5024254237889453</v>
+        <v>-0.4005887383419551</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>DR-202</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.214628170101724</v>
+        <v>1.30789603670721</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.2971878772404632</v>
+        <v>0.4981704585595624</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.668672070197128</v>
+        <v>0.2763662659230459</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.486748456838125</v>
+        <v>-1.124362973004354</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5584432361910213</v>
+        <v>-0.6579007114793336</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>DR-204</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.7577110518895174</v>
+        <v>0.7964883029118328</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6770766852845803</v>
+        <v>0.08305730931083473</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9871456474986489</v>
+        <v>0.560734227741415</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9630197824096084</v>
+        <v>0.05611101899677577</v>
       </c>
       <c r="F13" t="n">
-        <v>5.258072951557875</v>
+        <v>-0.2273489940514427</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>DR-205</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.8046715095559754</v>
+        <v>-0.2263271646789215</v>
       </c>
       <c r="C14" t="n">
-        <v>1.01174771821303</v>
+        <v>1.146329586333892</v>
       </c>
       <c r="D14" t="n">
-        <v>1.205127336220749</v>
+        <v>0.736525331410952</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9339885642532489</v>
+        <v>1.075992610055619</v>
       </c>
       <c r="F14" t="n">
-        <v>1.990367228103439</v>
+        <v>1.15007681594469</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>DR-206</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.838944508770059</v>
+        <v>1.435412400776923</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.02945105089770365</v>
+        <v>-0.9219534730808204</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4666587581009847</v>
+        <v>0.3177288785511732</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4499837240527063</v>
+        <v>0.1173132583136361</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6085945221855628</v>
+        <v>0.1981074367796686</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>DR-207</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.872074577432138</v>
+        <v>-0.8911572186129118</v>
       </c>
       <c r="C16" t="n">
-        <v>0.126728764468907</v>
+        <v>1.226439141452067</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5778739054081781</v>
+        <v>0.8864648021879096</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.112248084637795</v>
+        <v>0.3186978866804897</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2130000597115524</v>
+        <v>-0.3445405857773775</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>DR-208</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.120707254768808</v>
+        <v>-0.8911572186129118</v>
       </c>
       <c r="C17" t="n">
-        <v>0.156477300729213</v>
+        <v>-1.708483650604725</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4132754873935315</v>
+        <v>0.9019757819234575</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.00810526339142</v>
+        <v>1.075992610055619</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3343719865827171</v>
+        <v>0.9496622098046852</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>DR-209</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4632608474383942</v>
+        <v>-0.9934387653719873</v>
       </c>
       <c r="C18" t="n">
-        <v>3.42137915529787</v>
+        <v>-2.728059806654231</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.469421130808921</v>
+        <v>0.6951627187828247</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9045840973696732</v>
+        <v>0.3607509747675982</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0484163981648025</v>
+        <v>-0.3241594393902584</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t>DR-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.288106475224936</v>
+        <v>-0.7888756718538364</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.9516556749672103</v>
+        <v>-1.242391693553523</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1116600078964211</v>
+        <v>-0.05970496168048003</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1857092310148101</v>
+        <v>0.6159182608703522</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3530445907167424</v>
+        <v>-0.4566368909065326</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>DR-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.006343729226187198</v>
+        <v>0.5919252093936821</v>
       </c>
       <c r="C20" t="n">
-        <v>-2.714256448390379</v>
+        <v>-1.490003045736974</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.17487681615319</v>
+        <v>-0.2251554121929856</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7155231093001797</v>
+        <v>-0.3801250552046569</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9260287924639939</v>
+        <v>-0.3649217321644966</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>DR-18</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.7858873264893922</v>
+        <v>-0.9941099041302488</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0895430941435231</v>
+        <v>0.6146934478223631</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.21491426918378</v>
+        <v>0.1315971217246031</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9849926578443511</v>
+        <v>0.5699108259518253</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8572049023354268</v>
+        <v>-0.1288401198470336</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>DR-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.214628170101724</v>
+        <v>-0.2263271646789215</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2754714457704397</v>
+        <v>-1.045759149172546</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.477382016828756</v>
+        <v>-0.1837927995648601</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2635491846965469</v>
+        <v>-1.224379135870717</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2970267783146665</v>
+        <v>-0.6553530681809439</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>DR-20</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.6637901365566011</v>
+        <v>0.3873621158755312</v>
       </c>
       <c r="C23" t="n">
-        <v>1.755461124720696</v>
+        <v>-0.9365188467386708</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3865838520398056</v>
+        <v>-0.3027103108707236</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2273445550771351</v>
+        <v>-1.288057246484595</v>
       </c>
       <c r="F23" t="n">
-        <v>0.06708900229882786</v>
+        <v>-0.3980410950435651</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>DR-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.8046715095559754</v>
+        <v>-0.4308902581970723</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2234115073149029</v>
+        <v>-1.125868704290722</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3332005813323524</v>
+        <v>-0.4216278221765872</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.01446133291498942</v>
+        <v>0.7782974429357407</v>
       </c>
       <c r="F24" t="n">
-        <v>0.31916915810817</v>
+        <v>-0.3470882290757674</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>DR-38</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-1.104059834153946</v>
+        <v>-0.6354533517152232</v>
       </c>
       <c r="C25" t="n">
-        <v>-1.011152747487824</v>
+        <v>2.063948126778447</v>
       </c>
       <c r="D25" t="n">
-        <v>3.175859746504215</v>
+        <v>0.2453443064519518</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6889673478867212</v>
+        <v>-0.3778675084368125</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.3810534969177805</v>
+        <v>-0.5483520496485684</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>DR-40</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1901260070476558</v>
+        <v>-0.9422979919924495</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4688369314624329</v>
+        <v>1.044371970728941</v>
       </c>
       <c r="D26" t="n">
-        <v>0.453312940424121</v>
+        <v>-0.6956551308379231</v>
       </c>
       <c r="E26" t="n">
-        <v>0.411174520246268</v>
+        <v>0.3856849761544511</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.9940550815684888</v>
+        <v>0.04779648217466518</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>DR-44</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.7651063995535264</v>
+        <v>-0.4308902581970723</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5357711380481227</v>
+        <v>0.0903399961397609</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2807070318033546</v>
+        <v>0.5400529214273523</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5796775835123065</v>
+        <v>0.4806022758158619</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.3652418988364625</v>
+        <v>-0.3190641527934786</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>DR-45</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0052423154474271</v>
+        <v>-0.7888756718538364</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7440108918702703</v>
+        <v>0.5637146400198877</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.08051976665040683</v>
+        <v>0.1833003875097617</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7171644300125732</v>
+        <v>-0.1743270918478717</v>
       </c>
       <c r="F28" t="n">
-        <v>0.02498787572560004</v>
+        <v>-0.4795656805920415</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>DR-48</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.62152128744819</v>
+        <v>-0.2263271646789215</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4465255292672033</v>
+        <v>-0.09172717458336516</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7700536799550061</v>
+        <v>0.1833003875097617</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.01131318189062381</v>
+        <v>0.2660866406853601</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2177592502758582</v>
+        <v>0.1114875646344123</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>DR-49</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.9191761425537172</v>
+        <v>-0.8911572186129118</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5952682105687361</v>
+        <v>0.7093683765983892</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1783890962807365</v>
+        <v>-0.2251554121929856</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1285142447506927</v>
+        <v>0.4951239912851246</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.6266339787497387</v>
+        <v>-0.1432767652045764</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>DR-50</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.6726645537534119</v>
+        <v>-0.3797494848175346</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2903457139005927</v>
+        <v>0.4107782166124624</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.2451181846650535</v>
+        <v>-0.4526497816476813</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8233156750018572</v>
+        <v>0.1750730253507229</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6437561152484705</v>
+        <v>-0.5126850434711101</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>DR-51</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5802227079532976</v>
+        <v>0.1316582489778424</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5357711380481227</v>
+        <v>0.4763223980727877</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8189883447701709</v>
+        <v>-0.4061168424410392</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8250785245635092</v>
+        <v>0.1750730253507229</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.3910722032076218</v>
+        <v>-0.02353753018025173</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>DR-53</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.073245885553908</v>
+        <v>-0.3797494848175346</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2234115073149029</v>
+        <v>0.5928453873355884</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.757644188042883</v>
+        <v>-0.3285619437633012</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5815083312047504</v>
+        <v>0.301169572346345</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3397402516415051</v>
+        <v>0.6668738036834079</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>DR-55</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.073245885553908</v>
+        <v>-0.9934387653719873</v>
       </c>
       <c r="C34" t="n">
-        <v>-1.784614690255796</v>
+        <v>-0.222815537504017</v>
       </c>
       <c r="D34" t="n">
-        <v>1.222921759789899</v>
+        <v>1.548266604237932</v>
       </c>
       <c r="E34" t="n">
-        <v>0.6083328960752282</v>
+        <v>1.558741529709477</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0484163981648025</v>
+        <v>2.294817871354546</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>DR-56</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.9191761425537172</v>
+        <v>-0.02176407116077067</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3424056523561296</v>
+        <v>0.1995802985736355</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4889017875624237</v>
+        <v>0.1522784280386676</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8309945448384498</v>
+        <v>-0.9499883883991114</v>
       </c>
       <c r="F35" t="n">
-        <v>0.03993207803546656</v>
+        <v>-0.4973991836807707</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>DR-59</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9191761425537172</v>
+        <v>0.09313488425362379</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4390883952021268</v>
+        <v>0.3743647824678367</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2486770693788848</v>
+        <v>-0.3027103108707236</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6092307651364556</v>
+        <v>0.5798339981891552</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.247970307836784</v>
+        <v>0.4885387727961157</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9808040397537934</v>
+        <v>-0.9135732531388508</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4688369314624329</v>
+        <v>-0.1791194165304664</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1152188926102541</v>
+        <v>3.347540253561429</v>
       </c>
       <c r="E37" t="n">
-        <v>0.5840449897135376</v>
+        <v>0.5524025112119043</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.874870757404639</v>
+        <v>0.8146371149900213</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>DR-140</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.6110366565533357</v>
+        <v>-0.3095483707033662</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1707565981341599</v>
+        <v>0.1413188039422351</v>
       </c>
       <c r="D38" t="n">
-        <v>0.5378364523775886</v>
+        <v>-0.411287169019554</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6779270598802831</v>
+        <v>0.3866020632031352</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.586040371623325</v>
+        <v>-0.4102676103920652</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.5494087593532594</v>
+        <v>-0.645117749834191</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3349685182910531</v>
+        <v>0.6292588214802129</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4355185168549704</v>
+        <v>-0.488842067697292</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6534583114183262</v>
+        <v>0.626682398088123</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6252933605391255</v>
+        <v>-0.3909940191175275</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.04243193695387</v>
+        <v>-0.9135732531388508</v>
       </c>
       <c r="C40" t="n">
-        <v>0.401902724876743</v>
+        <v>0.6802376292826884</v>
       </c>
       <c r="D40" t="n">
-        <v>0.07518143957966451</v>
+        <v>0.3642618177578153</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4868588776911036</v>
+        <v>0.6340242653785469</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.8732388466070612</v>
+        <v>-0.5557624949841886</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.09768416124754148</v>
+        <v>-0.8464593773126861</v>
       </c>
       <c r="C41" t="n">
-        <v>0.03748315568798623</v>
+        <v>0.5491492663620379</v>
       </c>
       <c r="D41" t="n">
-        <v>0.4444157286395458</v>
+        <v>0.002338957261708186</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4732826051633641</v>
+        <v>0.3476936405463128</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.6715133067816732</v>
+        <v>-0.7725330187920911</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>DR-144</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.857548245353641</v>
+        <v>-0.645117749834191</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.05919958715800968</v>
+        <v>0.170449551257936</v>
       </c>
       <c r="D42" t="n">
-        <v>1.20067873032846</v>
+        <v>-0.6749738245238603</v>
       </c>
       <c r="E42" t="n">
-        <v>0.5538522834510141</v>
+        <v>-3.507301099812472</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.9027648211276217</v>
+        <v>-0.7032035812618</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>DR-157</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.09768416124754148</v>
+        <v>-0.6786746877472736</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.3641220838261531</v>
+        <v>0.4326262770992371</v>
       </c>
       <c r="D43" t="n">
-        <v>0.6223599643310544</v>
+        <v>-0.6284408853172182</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5461807577932011</v>
+        <v>0.3011282091625433</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.8184029536377057</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>S65</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>-0.857548245353641</v>
-      </c>
-      <c r="C44" t="n">
-        <v>0.2085372391847498</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0.177499375102281</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0.531520921665673</v>
-      </c>
-      <c r="F44" t="n">
-        <v>-0.754462918616618</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>S69</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>-0.857548245353641</v>
-      </c>
-      <c r="C45" t="n">
-        <v>0.5208968699179697</v>
-      </c>
-      <c r="D45" t="n">
-        <v>1.396417389589121</v>
-      </c>
-      <c r="E45" t="n">
-        <v>1.076510983296353</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.3391881876614418</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>S70</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>0.1901260070476558</v>
-      </c>
-      <c r="C46" t="n">
-        <v>0.63245388089412</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0.3776866402552304</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0.2192660462771809</v>
-      </c>
-      <c r="F46" t="n">
-        <v>-0.7087387142921362</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>S72</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>-0.1796413761528018</v>
-      </c>
-      <c r="C47" t="n">
-        <v>1.175364667644717</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0.9293137708989088</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0.2089216734643732</v>
-      </c>
-      <c r="F47" t="n">
-        <v>-0.3795971364549326</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>S74</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>0.2825678528477705</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-0.1558823300040069</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0.3999296697166678</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.7518146116931469</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.02634680551364223</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>S79</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>0.0052423154474271</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-0.05176245309293317</v>
-      </c>
-      <c r="D49" t="n">
-        <v>-0.2317723669881898</v>
-      </c>
-      <c r="E49" t="n">
-        <v>-0.08453536202453302</v>
-      </c>
-      <c r="F49" t="n">
-        <v>-0.2902694706916244</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>-0.4877808621531832</v>
-      </c>
-      <c r="C50" t="n">
-        <v>0.2754714457704397</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0.04404119833365024</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0.6755708509647458</v>
-      </c>
-      <c r="F50" t="n">
-        <v>-0.4423617126355753</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>S81</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>-0.6726645537534119</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-0.1781937321992364</v>
-      </c>
-      <c r="D51" t="n">
-        <v>-0.4052679967874117</v>
-      </c>
-      <c r="E51" t="n">
-        <v>-3.500423767742475</v>
-      </c>
-      <c r="F51" t="n">
-        <v>-0.5003925896471096</v>
+        <v>-0.6237069343765819</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_standardized_matrix.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_standardized_matrix.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,921 +467,1295 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.1751863912993838</v>
+        <v>0.02737043202415234</v>
       </c>
       <c r="C2" t="n">
-        <v>1.219156454623142</v>
+        <v>1.401026011880257</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.401862901748136</v>
+        <v>-2.029541522400534</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.057489420970179</v>
+        <v>-0.7158140251878977</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7445205836245899</v>
+        <v>-0.7186388594902738</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>DR-10</t>
+          <t>DR-94</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8476290762913705</v>
+        <v>-0.7747738406500133</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.2737943453064912</v>
+        <v>-0.2705265835914633</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9381680679730683</v>
+        <v>0.5103511161782069</v>
       </c>
       <c r="E3" t="n">
-        <v>0.451200284001553</v>
+        <v>-1.009072061629796</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5432567630517888</v>
+        <v>0.1226645429019804</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>DR-54</t>
+          <t>DR-103</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.949910623050446</v>
+        <v>0.4045725964738481</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.4995576370031679</v>
+        <v>-1.806547887538452</v>
       </c>
       <c r="D4" t="n">
-        <v>0.958849374287131</v>
+        <v>1.477242063818982</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4124832255437746</v>
+        <v>-0.8480117942465809</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6196860620034853</v>
+        <v>-1.016172989604608</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>DR-163</t>
+          <t>SCR-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.819303770502587</v>
+        <v>-0.6332522681951499</v>
       </c>
       <c r="C5" t="n">
-        <v>1.146329586333892</v>
+        <v>0.8724539749337953</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.970598825384873</v>
+        <v>-0.440665502471444</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.08171081763279836</v>
+        <v>0.5562007387424492</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5891143424228067</v>
+        <v>2.00656168039755</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>DR-164</t>
+          <t>SCR-02</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.739837691334266</v>
+        <v>0.8763111713233926</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1850149249157858</v>
+        <v>-0.7268152650580697</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.802105018640304</v>
+        <v>-0.1765743928919499</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.533170455457239</v>
+        <v>-2.748723204855355</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4821133238904314</v>
+        <v>-0.392367424419386</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>DR-167</t>
+          <t>LSC-07</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.819303770502587</v>
+        <v>-0.2086875508305598</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.7303317110915</v>
+        <v>1.102857170525843</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5250343537469027</v>
+        <v>0.2087388653469847</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2636356419838351</v>
+        <v>0.2374854045621987</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5738284826324674</v>
+        <v>0.3670669091100285</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>DR-168</t>
+          <t>DR-125</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.63755614457519</v>
+        <v>1.112180458748165</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.511851106223749</v>
+        <v>-1.038537235564956</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5560563132179968</v>
+        <v>-1.178100240149704</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.389434896742562</v>
+        <v>-1.807885465880997</v>
       </c>
       <c r="F8" t="n">
-        <v>3.935500155517633</v>
+        <v>-0.1851293848025029</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>DR-175</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4896436626346066</v>
+        <v>-1.010643128074786</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.191412885751047</v>
+        <v>-1.201174785394639</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4423091284906499</v>
+        <v>2.784709524360085</v>
       </c>
       <c r="E9" t="n">
-        <v>1.075992610055619</v>
+        <v>0.4624860111775051</v>
       </c>
       <c r="F9" t="n">
-        <v>3.204326528879736</v>
+        <v>5.560357265681184</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>DR-195</t>
+          <t>LSC-12</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.7888756718538364</v>
+        <v>-1.293686272984512</v>
       </c>
       <c r="C10" t="n">
-        <v>1.335679443885943</v>
+        <v>-2.068575051152938</v>
       </c>
       <c r="D10" t="n">
-        <v>1.196684396898858</v>
+        <v>2.901602310567402</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7324981864557588</v>
+        <v>0.4228366307240621</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.02353753018025173</v>
+        <v>-0.42110472937594</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>DR-197</t>
+          <t>SCR-04</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.001051396429983</v>
+        <v>0.6876157413835747</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3161032878364363</v>
+        <v>0.6284976501892717</v>
       </c>
       <c r="D11" t="n">
-        <v>0.338410184865236</v>
+        <v>0.2520324898682124</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2697348657726139</v>
+        <v>0.228439692863152</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4005887383419551</v>
+        <v>-1.094741050888993</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>DR-202</t>
+          <t>SCR-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.30789603670721</v>
+        <v>-0.7747738406500133</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4981704585595624</v>
+        <v>0.7504758125615323</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2763662659230459</v>
+        <v>-0.4623123147320586</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.124362973004354</v>
+        <v>0.3463566304505318</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6579007114793336</v>
+        <v>-0.4037291351924258</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>DR-204</t>
+          <t>DR-141</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7964883029118328</v>
+        <v>1.819788321022482</v>
       </c>
       <c r="C13" t="n">
-        <v>0.08305730931083473</v>
+        <v>0.09992561324281021</v>
       </c>
       <c r="D13" t="n">
-        <v>0.560734227741415</v>
+        <v>-0.7134153369551852</v>
       </c>
       <c r="E13" t="n">
-        <v>0.05611101899677577</v>
+        <v>-0.001629463595240271</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2273489940514427</v>
+        <v>0.3116832204964367</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>DR-205</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.2263271646789215</v>
+        <v>-0.7747738406500133</v>
       </c>
       <c r="C14" t="n">
-        <v>1.146329586333892</v>
+        <v>0.723369554256586</v>
       </c>
       <c r="D14" t="n">
-        <v>0.736525331410952</v>
+        <v>-0.8043319484497656</v>
       </c>
       <c r="E14" t="n">
-        <v>1.075992610055619</v>
+        <v>-2.497766470167082</v>
       </c>
       <c r="F14" t="n">
-        <v>1.15007681594469</v>
+        <v>-0.1859672301884925</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>DR-206</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.435412400776923</v>
+        <v>-0.7747738406500133</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.9219534730808204</v>
+        <v>-1.268940431157005</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3177288785511732</v>
+        <v>-0.05968160668463292</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1173132583136361</v>
+        <v>0.334530209818342</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1981074367796686</v>
+        <v>-0.4795631777668459</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>DR-207</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.8911572186129118</v>
+        <v>1.58391903359771</v>
       </c>
       <c r="C16" t="n">
-        <v>1.226439141452067</v>
+        <v>0.249010033920017</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8864648021879096</v>
+        <v>0.1264809787566499</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3186978866804897</v>
+        <v>0.4399528494179898</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3445405857773775</v>
+        <v>-0.2989509204934456</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>DR-208</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.8911572186129118</v>
+        <v>-0.06716597837569646</v>
       </c>
       <c r="C17" t="n">
-        <v>-1.708483650604725</v>
+        <v>0.723369554256586</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9019757819234575</v>
+        <v>-0.3713957032374798</v>
       </c>
       <c r="E17" t="n">
-        <v>1.075992610055619</v>
+        <v>-2.515666795816752</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9496622098046852</v>
+        <v>0.4848039110102405</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>DR-209</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.9934387653719873</v>
+        <v>0.4045725964738481</v>
       </c>
       <c r="C18" t="n">
-        <v>-2.728059806654231</v>
+        <v>1.129963428830789</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6951627187828247</v>
+        <v>-0.2674910043865303</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3607509747675982</v>
+        <v>0.4425686967692404</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3241594393902584</v>
+        <v>0.02510001706929636</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>DR-15</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.7888756718538364</v>
+        <v>-0.3502091232854233</v>
       </c>
       <c r="C19" t="n">
-        <v>-1.242391693553523</v>
+        <v>0.2896694213774364</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.05970496168048003</v>
+        <v>0.161115878373632</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6159182608703522</v>
+        <v>-2.768600152893506</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4566368909065326</v>
+        <v>0.1638324849419587</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>DR-17</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5919252093936821</v>
+        <v>0.1687033090490758</v>
       </c>
       <c r="C20" t="n">
-        <v>-1.490003045736974</v>
+        <v>1.075750912220895</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2251554121929856</v>
+        <v>0.3213022891021782</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3801250552046569</v>
+        <v>-0.06323108531693668</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3649217321644966</v>
+        <v>0.719641751157704</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>DR-18</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.9941099041302488</v>
+        <v>1.348049746172937</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6146934478223631</v>
+        <v>0.5878382627318524</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1315971217246031</v>
+        <v>-0.9385421844655737</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5699108259518253</v>
+        <v>-0.06721342488258492</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1288401198470336</v>
+        <v>0.236939273111423</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>DR-19</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.2263271646789215</v>
+        <v>1.348049746172937</v>
       </c>
       <c r="C22" t="n">
-        <v>-1.045759149172546</v>
+        <v>-3.098612866740916</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1837927995648601</v>
+        <v>0.8797900454260266</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.224379135870717</v>
+        <v>0.4386438918794693</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6553530681809439</v>
+        <v>0.1124047453118309</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>DR-20</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3873621158755312</v>
+        <v>-1.010643128074786</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.9365188467386708</v>
+        <v>0.8589008457813198</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3027103108707236</v>
+        <v>-0.3627369783332327</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.288057246484595</v>
+        <v>-0.1492296811249172</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3980410950435651</v>
+        <v>-0.690976678419836</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>DR-23</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.4308902581970723</v>
+        <v>-0.6332522681951499</v>
       </c>
       <c r="C24" t="n">
-        <v>-1.125868704290722</v>
+        <v>0.3032225505299095</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4216278221765872</v>
+        <v>-0.4276774151150765</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7782974429357407</v>
+        <v>0.5168523892292507</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3470882290757674</v>
+        <v>0.7050733991590065</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>DR-38</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.6354533517152232</v>
+        <v>-0.9162954131048767</v>
       </c>
       <c r="C25" t="n">
-        <v>2.063948126778447</v>
+        <v>0.1405850007002296</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2453443064519518</v>
+        <v>-4.32410362202565</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.3778675084368125</v>
+        <v>0.6644918298942235</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5483520496485684</v>
+        <v>-0.01333396480775942</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>DR-40</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.9422979919924495</v>
+        <v>-0.4917306957402865</v>
       </c>
       <c r="C26" t="n">
-        <v>1.044371970728941</v>
+        <v>0.7504758125615323</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6956551308379231</v>
+        <v>-0.9861651714389249</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3856849761544511</v>
+        <v>0.5180860155960846</v>
       </c>
       <c r="F26" t="n">
-        <v>0.04779648217466518</v>
+        <v>-0.4321144308520855</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>DR-44</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.4308902581970723</v>
+        <v>-1.246512415499558</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0903399961397609</v>
+        <v>0.181244388157649</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5400529214273523</v>
+        <v>-1.899660648836848</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4806022758158619</v>
+        <v>0.3476377713224181</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.3190641527934786</v>
+        <v>0.3709859625686035</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>DR-45</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.7888756718538364</v>
+        <v>-1.246512415499558</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5637146400198877</v>
+        <v>-3.478100483010172</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1833003875097617</v>
+        <v>1.001012194085467</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1743270918478717</v>
+        <v>0.366409362059892</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.4795656805920415</v>
+        <v>0.05084595977093423</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>DR-48</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2263271646789215</v>
+        <v>-1.010643128074786</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.09172717458336516</v>
+        <v>0.3980944545972238</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1833003875097617</v>
+        <v>0.286667389485196</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2660866406853601</v>
+        <v>0.5222259937068947</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1114875646344123</v>
+        <v>0.04152241747418529</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>DR-49</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.8911572186129118</v>
+        <v>-1.010643128074786</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7093683765983892</v>
+        <v>0.5742851335793793</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.2251554121929856</v>
+        <v>0.05288181707056053</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4951239912851246</v>
+        <v>0.3670376828037543</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1432767652045764</v>
+        <v>-0.2748576850084588</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>DR-50</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3797494848175346</v>
+        <v>-1.104990843044694</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4107782166124624</v>
+        <v>0.6284976501892717</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4526497816476813</v>
+        <v>-0.076999056493124</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1750730253507229</v>
+        <v>0.3494129022741261</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.5126850434711101</v>
+        <v>-0.9637676705224428</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>DR-51</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.1316582489778424</v>
+        <v>-0.538904553225241</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4763223980727877</v>
+        <v>-0.5370714569234412</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.4061168424410392</v>
+        <v>0.3342903764585473</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1750730253507229</v>
+        <v>0.415110735855632</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.02353753018025173</v>
+        <v>-0.6463677754964203</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>DR-53</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3797494848175346</v>
+        <v>0.6876157413835747</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5928453873355884</v>
+        <v>0.547178875274433</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.3285619437633012</v>
+        <v>-0.06834033158887846</v>
       </c>
       <c r="E33" t="n">
-        <v>0.301169572346345</v>
+        <v>-0.1297971681810568</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6668738036834079</v>
+        <v>-0.01822416149748947</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>DR-55</t>
+          <t>LSC-30</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9934387653719873</v>
+        <v>-0.538904553225241</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.222815537504017</v>
+        <v>0.1134787423952833</v>
       </c>
       <c r="D34" t="n">
-        <v>1.548266604237932</v>
+        <v>0.2650205772245814</v>
       </c>
       <c r="E34" t="n">
-        <v>1.558741529709477</v>
+        <v>0.870773913517998</v>
       </c>
       <c r="F34" t="n">
-        <v>2.294817871354546</v>
+        <v>2.509684649430614</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>DR-56</t>
+          <t>LSC-32</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.02176407116077067</v>
+        <v>3.235004045571116</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1995802985736355</v>
+        <v>0.9673258790011071</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1522784280386676</v>
+        <v>0.2996554768415636</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.9499883883991114</v>
+        <v>0.4938301224612287</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.4973991836807707</v>
+        <v>0.4843712926379504</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>DR-59</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.09313488425362379</v>
+        <v>1.819788321022482</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3743647824678367</v>
+        <v>-1.065643493869905</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.3027103108707236</v>
+        <v>0.4252069879531277</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5798339981891552</v>
+        <v>0.6665875371275516</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4885387727961157</v>
+        <v>1.153279887599046</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>LSC-09</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9135732531388508</v>
+        <v>-0.444556838255332</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1791194165304664</v>
+        <v>0.3845413254447507</v>
       </c>
       <c r="D37" t="n">
-        <v>3.347540253561429</v>
+        <v>0.2347150400597213</v>
       </c>
       <c r="E37" t="n">
-        <v>0.5524025112119043</v>
+        <v>0.3979877243844726</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8146371149900213</v>
+        <v>0.6847844105514359</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>DR-140</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.3095483707033662</v>
+        <v>-1.199338558014603</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1413188039422351</v>
+        <v>0.5065194878170112</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.411287169019554</v>
+        <v>-0.1159633185622297</v>
       </c>
       <c r="E38" t="n">
-        <v>0.3866020632031352</v>
+        <v>0.2814029297336496</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.4102676103920652</v>
+        <v>-0.9619743401065938</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>LSC-17</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.645117749834191</v>
+        <v>0.5460941689287114</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6292588214802129</v>
+        <v>-0.1575838406541864</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.488842067697292</v>
+        <v>0.2433737649639669</v>
       </c>
       <c r="E39" t="n">
-        <v>0.626682398088123</v>
+        <v>0.2719023755639297</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.3909940191175275</v>
+        <v>-0.7402952221306757</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>LSC-24</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.9135732531388508</v>
+        <v>-0.9162954131048767</v>
       </c>
       <c r="C40" t="n">
-        <v>0.6802376292826884</v>
+        <v>-0.3337745196363395</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3642618177578153</v>
+        <v>0.9793653818248526</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6340242653785469</v>
+        <v>0.3282843162950626</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.5557624949841886</v>
+        <v>-0.9944208612301106</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>LSC-53</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.8464593773126861</v>
+        <v>0.5460941689287114</v>
       </c>
       <c r="C41" t="n">
-        <v>0.5491492663620379</v>
+        <v>-0.8894528148877496</v>
       </c>
       <c r="D41" t="n">
-        <v>0.002338957261708186</v>
+        <v>0.4165482630488806</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3476936405463128</v>
+        <v>0.322915851208086</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.7725330187920911</v>
+        <v>-0.9017143829519831</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>DR-144</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.645117749834191</v>
+        <v>0.6876157413835747</v>
       </c>
       <c r="C42" t="n">
-        <v>0.170449551257936</v>
+        <v>-0.686155877600648</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.6749738245238603</v>
+        <v>0.4641712500222333</v>
       </c>
       <c r="E42" t="n">
-        <v>-3.507301099812472</v>
+        <v>0.4009832198433276</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.7032035812618</v>
+        <v>0.3031174559420027</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
+          <t>LSC-45</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1.112180458748165</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.1711369698066595</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-0.3713957032374798</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.180831588807663</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.6524191895912486</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>LSC-47</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2.102831465932208</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.4150932945511806</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.5291116868040756</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.301774952110327</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.1469001913275854</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>LSC-48</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.8763111713233926</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.9978778481075371</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.1308103412087719</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.283758463776653</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.1394844735155864</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>LSC-53</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>-0.9162954131048767</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.1541381298527027</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-0.01638798216340526</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.312657028916163</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-0.8314497522111602</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>LSC-55</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.2630510240189848</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.04915880743439899</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.1178222538524043</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1.060228334719891</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.410702723143749</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>LSC-56</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>-0.06716597837569646</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.686155877600648</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.5810640362295504</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.6230495845892515</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-0.03702583663933803</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>LSC-57</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>-0.9162954131048767</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.723369554256586</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.169857329718259</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.6940362029053364</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.3703792914635335</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>LSC-58</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0.6876157413835747</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.9266664915436877</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.1784333281821246</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.09414385806414712</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-0.7812027617032876</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>LSC-59</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0.1215294515641213</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1.916044919674248</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.7152742722453584</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.08690495842810542</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-0.4195043137660051</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>LSC-60</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0.8291373138384384</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.5099651986184949</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.2000801404427377</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.4668165842047864</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.02659336469927494</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>LSC-62</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0.4045725964738481</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.3202213904838663</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-0.4146893277587075</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-0.1184536520779219</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-0.3213408478290776</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>SCR-08</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>-0.3502091232854233</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.2761162922249633</v>
+      </c>
+      <c r="D54" t="n">
+        <v>-0.1462688557270898</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.4134618819164155</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-0.4884772157589837</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>DR-144</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>-0.6332522681951499</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.5506245860759142</v>
+      </c>
+      <c r="D55" t="n">
+        <v>-0.5835344633914992</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-2.508861827070899</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-0.5522481871611229</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>DR-145</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>-0.3030352658004687</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.6013913918843256</v>
+      </c>
+      <c r="D56" t="n">
+        <v>-0.886589835040099</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-0.01859935666749868</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-0.3574165518823844</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>SCR-09</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1.112180458748165</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.2083506464625976</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-0.1462688557270898</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.3943841935513224</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-0.7279495128099593</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>DR-156</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>-1.05781698555974</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.5065194878170112</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.2303856776075978</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.2409610723729339</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-0.9455531650510192</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
           <t>DR-157</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>-0.6786746877472736</v>
-      </c>
-      <c r="C43" t="n">
-        <v>0.4326262770992371</v>
-      </c>
-      <c r="D43" t="n">
-        <v>-0.6284408853172182</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0.3011282091625433</v>
-      </c>
-      <c r="F43" t="n">
-        <v>-0.6237069343765819</v>
+      <c r="B59" t="n">
+        <v>-0.6804261256801044</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.06271193658687212</v>
+      </c>
+      <c r="D59" t="n">
+        <v>-0.5445702013223935</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.2785752074000461</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-0.2321015219457077</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>DR-159</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>-0.9162954131048767</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1.089304041373368</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.3342903764585473</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-2.474461711450562</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-0.6325187280595805</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_standardized_matrix.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_standardized_matrix.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02737043202415234</v>
+        <v>0.1625449618446163</v>
       </c>
       <c r="C2" t="n">
-        <v>1.401026011880257</v>
+        <v>1.346644582623407</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.029541522400534</v>
+        <v>-1.923367007889838</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.7158140251878977</v>
+        <v>-0.6173405082582101</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7186388594902738</v>
+        <v>-0.6769844169493342</v>
       </c>
     </row>
     <row r="3">
@@ -489,19 +489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.7747738406500133</v>
+        <v>-0.7817374198451194</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.2705265835914633</v>
+        <v>-0.2553737052436774</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5103511161782069</v>
+        <v>0.4881537823405614</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.009072061629796</v>
+        <v>-0.9047558306178681</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1226645429019804</v>
+        <v>0.1702984827450448</v>
       </c>
     </row>
     <row r="4">
@@ -511,19 +511,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4045725964738481</v>
+        <v>0.6065864770169949</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.806547887538452</v>
+        <v>-1.727498618418839</v>
       </c>
       <c r="D4" t="n">
-        <v>1.477242063818982</v>
+        <v>1.406175901348729</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8480117942465809</v>
+        <v>-0.7469044406579175</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.016172989604608</v>
+        <v>-0.9766332473290535</v>
       </c>
     </row>
     <row r="5">
@@ -533,19 +533,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.6332522681951499</v>
+        <v>-0.6151385522216656</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8724539749337953</v>
+        <v>0.8400604213248978</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.440665502471444</v>
+        <v>-0.4147963317286595</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5562007387424492</v>
+        <v>0.6293313233378477</v>
       </c>
       <c r="F5" t="n">
-        <v>2.00656168039755</v>
+        <v>2.067585269942616</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8763111713233926</v>
+        <v>1.161916035761841</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.7268152650580697</v>
+        <v>-0.6926814000398291</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1765743928919499</v>
+        <v>-0.164052976835385</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.748723204855355</v>
+        <v>-2.60974710789045</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.392367424419386</v>
+        <v>-0.3483940334940475</v>
       </c>
     </row>
     <row r="7">
@@ -577,19 +577,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.2086875508305598</v>
+        <v>-0.1153419493513044</v>
       </c>
       <c r="C7" t="n">
-        <v>1.102857170525843</v>
+        <v>1.060879158301172</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2087388653469847</v>
+        <v>0.2017856885007046</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2374854045621987</v>
+        <v>0.3169659006343107</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3670669091100285</v>
+        <v>0.4164379194144966</v>
       </c>
     </row>
     <row r="8">
@@ -599,19 +599,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.112180458748165</v>
+        <v>1.439580815134263</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.038537235564956</v>
+        <v>-0.9914361618312568</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.178100240149704</v>
+        <v>-1.114959470255782</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.807885465880997</v>
+        <v>-1.687654109804711</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1851293848025029</v>
+        <v>-0.1396830659236304</v>
       </c>
     </row>
     <row r="9">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1.010643128074786</v>
+        <v>-1.059402199217542</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.201174785394639</v>
+        <v>-1.147308211461569</v>
       </c>
       <c r="D9" t="n">
-        <v>2.784709524360085</v>
+        <v>2.647561035410515</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4624860111775051</v>
+        <v>0.5374837171827732</v>
       </c>
       <c r="F9" t="n">
-        <v>5.560357265681184</v>
+        <v>5.64663917589164</v>
       </c>
     </row>
     <row r="10">
@@ -643,19 +643,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-1.293686272984512</v>
+        <v>-1.39259993446445</v>
       </c>
       <c r="C10" t="n">
-        <v>-2.068575051152938</v>
+        <v>-1.978625809489895</v>
       </c>
       <c r="D10" t="n">
-        <v>2.901602310567402</v>
+        <v>2.758545799051801</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4228366307240621</v>
+        <v>0.498624289483356</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.42110472937594</v>
+        <v>-0.3773355865696147</v>
       </c>
     </row>
     <row r="11">
@@ -665,19 +665,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6876157413835747</v>
+        <v>0.939784212263902</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6284976501892717</v>
+        <v>0.6062523468794293</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2520324898682124</v>
+        <v>0.2428911565159946</v>
       </c>
       <c r="E11" t="n">
-        <v>0.228439692863152</v>
+        <v>0.3081004107896048</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.094741050888993</v>
+        <v>-1.055759724886506</v>
       </c>
     </row>
     <row r="12">
@@ -687,1075 +687,921 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.7747738406500133</v>
+        <v>-0.7817374198451194</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7504758125615323</v>
+        <v>0.7231563841021623</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4623123147320586</v>
+        <v>-0.4353490657363053</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3463566304505318</v>
+        <v>0.4236680352596511</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4037291351924258</v>
+        <v>-0.3598364967265706</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>DR-141</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.819788321022482</v>
+        <v>-0.7817374198451194</v>
       </c>
       <c r="C13" t="n">
-        <v>0.09992561324281021</v>
+        <v>0.6971777091637777</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.7134153369551852</v>
+        <v>-0.7600822630571049</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.001629463595240271</v>
+        <v>-2.363790299088561</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3116832204964367</v>
+        <v>-0.1405268662293444</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>DR-143</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.7747738406500133</v>
+        <v>-0.7817374198451194</v>
       </c>
       <c r="C14" t="n">
-        <v>0.723369554256586</v>
+        <v>-1.212254898807531</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.8043319484497656</v>
+        <v>-0.05306821319409968</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.497766470167082</v>
+        <v>0.4120772378185887</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1859672301884925</v>
+        <v>-0.436209523752609</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>SCR-11</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.7747738406500133</v>
+        <v>1.994910373879109</v>
       </c>
       <c r="C15" t="n">
-        <v>-1.268940431157005</v>
+        <v>0.2425508977420378</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.05968160668463292</v>
+        <v>0.1236852992716513</v>
       </c>
       <c r="E15" t="n">
-        <v>0.334530209818342</v>
+        <v>0.5153994939182676</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4795631777668459</v>
+        <v>-0.2543135791649461</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SCR-14</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.58391903359771</v>
+        <v>0.05125691827214916</v>
       </c>
       <c r="C16" t="n">
-        <v>0.249010033920017</v>
+        <v>0.6971777091637777</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1264809787566499</v>
+        <v>-0.3490275829041954</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4399528494179898</v>
+        <v>-2.381333988357456</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2989509204934456</v>
+        <v>0.5350117277310629</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>SCR-17</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.06716597837569646</v>
+        <v>0.6065864770169949</v>
       </c>
       <c r="C17" t="n">
-        <v>0.723369554256586</v>
+        <v>1.086857833239556</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3713957032374798</v>
+        <v>-0.2503744596674964</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.515666795816752</v>
+        <v>0.5179632245454837</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4848039110102405</v>
+        <v>0.07204052477201671</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>SCR-18</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4045725964738481</v>
+        <v>-0.2819408169747583</v>
       </c>
       <c r="C18" t="n">
-        <v>1.129963428830789</v>
+        <v>0.2815189101496147</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2674910043865303</v>
+        <v>0.1565696736838833</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4425686967692404</v>
+        <v>-2.629228038395292</v>
       </c>
       <c r="F18" t="n">
-        <v>0.02510001706929636</v>
+        <v>0.2117590226726129</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>SCR-19</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.3502091232854233</v>
+        <v>0.328921697644572</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2896694213774364</v>
+        <v>1.034900483362785</v>
       </c>
       <c r="D19" t="n">
-        <v>0.161115878373632</v>
+        <v>0.3086599053404602</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.768600152893506</v>
+        <v>0.02224072301892923</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1638324849419587</v>
+        <v>0.7715186592284551</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>SCR-20</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1687033090490758</v>
+        <v>1.717245594506686</v>
       </c>
       <c r="C20" t="n">
-        <v>1.075750912220895</v>
+        <v>0.5672843344718523</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3213022891021782</v>
+        <v>-0.8875092139045062</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.06323108531693668</v>
+        <v>0.01833772542713712</v>
       </c>
       <c r="F20" t="n">
-        <v>0.719641751157704</v>
+        <v>0.285385411549008</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>LSC-14</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.348049746172937</v>
+        <v>1.717245594506686</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5878382627318524</v>
+        <v>-2.96581545714853</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9385421844655737</v>
+        <v>0.838920442737713</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.06721342488258492</v>
+        <v>0.5141166153398881</v>
       </c>
       <c r="F21" t="n">
-        <v>0.236939273111423</v>
+        <v>0.159965764456089</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>LSC-15</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.348049746172937</v>
+        <v>-1.059402199217542</v>
       </c>
       <c r="C22" t="n">
-        <v>-3.098612866740916</v>
+        <v>0.8270710838557032</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8797900454260266</v>
+        <v>-0.340806489301136</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4386438918794693</v>
+        <v>-0.06204448340379655</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1124047453118309</v>
+        <v>-0.6491256291177548</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>LSC-16</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-1.010643128074786</v>
+        <v>-0.6151385522216656</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8589008457813198</v>
+        <v>0.294508247618807</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3627369783332327</v>
+        <v>-0.4024646913240733</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1492296811249172</v>
+        <v>0.5907669290014725</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.690976678419836</v>
+        <v>0.7568467638217257</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>LSC-17</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.6332522681951499</v>
+        <v>-0.948336287468573</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3032225505299095</v>
+        <v>0.138636197988497</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4276774151150765</v>
+        <v>-4.101956812700258</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5168523892292507</v>
+        <v>0.7354648815165094</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7050733991590065</v>
+        <v>0.03333337641270224</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>LSC-18</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.9162954131048767</v>
+        <v>-0.4485396845982119</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1405850007002296</v>
+        <v>0.7231563841021623</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.32410362202565</v>
+        <v>-0.932725228721326</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6644918298942235</v>
+        <v>0.5919759772655775</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.01333396480775942</v>
+        <v>-0.3884235386270447</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>LSC-19</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.4917306957402865</v>
+        <v>-1.337066978589965</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7504758125615323</v>
+        <v>0.1776042103960739</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.9861651714389249</v>
+        <v>-1.800050603843965</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5180860155960846</v>
+        <v>0.4249236513755772</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.4321144308520855</v>
+        <v>0.4203848272351433</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>LSC-22</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.246512415499558</v>
+        <v>-1.337066978589965</v>
       </c>
       <c r="C27" t="n">
-        <v>0.181244388157649</v>
+        <v>-3.329516906285923</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.899660648836848</v>
+        <v>0.9540157531805281</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3476377713224181</v>
+        <v>0.4433212471191591</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3709859625686035</v>
+        <v>0.09796945472235387</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>LSC-23</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.246512415499558</v>
+        <v>-1.059402199217542</v>
       </c>
       <c r="C28" t="n">
-        <v>-3.478100483010172</v>
+        <v>0.3854336099031554</v>
       </c>
       <c r="D28" t="n">
-        <v>1.001012194085467</v>
+        <v>0.2757755309282282</v>
       </c>
       <c r="E28" t="n">
-        <v>0.366409362059892</v>
+        <v>0.5960334726976462</v>
       </c>
       <c r="F28" t="n">
-        <v>0.05084595977093423</v>
+        <v>0.0885796460871459</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>LSC-24</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.010643128074786</v>
+        <v>-1.059402199217542</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3980944545972238</v>
+        <v>0.5542949970026601</v>
       </c>
       <c r="D29" t="n">
-        <v>0.286667389485196</v>
+        <v>0.05380600364565596</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5222259937068947</v>
+        <v>0.4439370495412633</v>
       </c>
       <c r="F29" t="n">
-        <v>0.04152241747418529</v>
+        <v>-0.2300491029169095</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>LSC-25</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.010643128074786</v>
+        <v>-1.170468110966511</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5742851335793793</v>
+        <v>0.6062523468794293</v>
       </c>
       <c r="D30" t="n">
-        <v>0.05288181707056053</v>
+        <v>-0.06951040040021569</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3670376828037543</v>
+        <v>0.426663415580869</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2748576850084588</v>
+        <v>-0.9238554615919605</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>LSC-26</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.104990843044694</v>
+        <v>-0.5040726404726965</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6284976501892717</v>
+        <v>-0.5108306754711323</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.076999056493124</v>
+        <v>0.320991545745048</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3494129022741261</v>
+        <v>0.4910523211544791</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.9637676705224428</v>
+        <v>-0.6041996719497911</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>LSC-27</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.538904553225241</v>
+        <v>0.939784212263902</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.5370714569234412</v>
+        <v>0.5283163220642755</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3342903764585473</v>
+        <v>-0.06128930679715769</v>
       </c>
       <c r="E32" t="n">
-        <v>0.415110735855632</v>
+        <v>-0.04299913330944569</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.6463677754964203</v>
+        <v>0.02840842303729856</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>SCR-06</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6876157413835747</v>
+        <v>2.272575153251532</v>
       </c>
       <c r="C33" t="n">
-        <v>0.547178875274433</v>
+        <v>-1.017414836769644</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.06834033158887846</v>
+        <v>0.4073130285771593</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.1297971681810568</v>
+        <v>0.7375188350154369</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.01822416149748947</v>
+        <v>1.208238844380852</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>LSC-30</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.538904553225241</v>
+        <v>-0.3930067287237273</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1134787423952833</v>
+        <v>0.3724442724339632</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2650205772245814</v>
+        <v>0.2264489693098786</v>
       </c>
       <c r="E34" t="n">
-        <v>0.870773913517998</v>
+        <v>0.4742704592779454</v>
       </c>
       <c r="F34" t="n">
-        <v>2.509684649430614</v>
+        <v>0.736413572834494</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>LSC-32</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.235004045571116</v>
+        <v>-1.28153402271548</v>
       </c>
       <c r="C35" t="n">
-        <v>0.9673258790011071</v>
+        <v>0.4893483096566962</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2996554768415636</v>
+        <v>-0.1065053216139775</v>
       </c>
       <c r="E35" t="n">
-        <v>0.4938301224612287</v>
+        <v>0.3600084368510182</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4843712926379504</v>
+        <v>-0.9220493852222107</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>LSC-37</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.819788321022482</v>
+        <v>0.7731853446404484</v>
       </c>
       <c r="C36" t="n">
-        <v>-1.065643493869905</v>
+        <v>-0.1471292263337407</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4252069879531277</v>
+        <v>0.2346700629129366</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6665875371275516</v>
+        <v>0.3506971665703607</v>
       </c>
       <c r="F36" t="n">
-        <v>1.153279887599046</v>
+        <v>-0.6987947004720406</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>LSC-38</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.444556838255332</v>
+        <v>-0.948336287468573</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3845413254447507</v>
+        <v>-0.315990613433243</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2347150400597213</v>
+        <v>0.9334630191728823</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3979877243844726</v>
+        <v>0.4059557840906765</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6847844105514359</v>
+        <v>-0.9547265174248813</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>LSC-39</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.199338558014603</v>
+        <v>0.7731853446404484</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5065194878170112</v>
+        <v>-0.8485534496701391</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1159633185622297</v>
+        <v>0.3990919349740998</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2814029297336496</v>
+        <v>0.4006942773907377</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.9619743401065938</v>
+        <v>-0.8613611351946513</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>LSC-40</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5460941689287114</v>
+        <v>0.939784212263902</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1575838406541864</v>
+        <v>-0.65371338763225</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2433737649639669</v>
+        <v>0.4443079497909211</v>
       </c>
       <c r="E39" t="n">
-        <v>0.2719023755639297</v>
+        <v>0.4772062741097559</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.7402952221306757</v>
+        <v>0.352033950572811</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>LSC-41</t>
+          <t>LSC-45</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.9162954131048767</v>
+        <v>1.439580815134263</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3337745196363395</v>
+        <v>-0.160118563802933</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9793653818248526</v>
+        <v>-0.3490275829041954</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3282843162950626</v>
+        <v>1.24151736708792</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.9944208612301106</v>
+        <v>0.703818318629625</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>LSC-42</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5460941689287114</v>
+        <v>-0.948336287468573</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.8894528148877496</v>
+        <v>0.1516255354576893</v>
       </c>
       <c r="D41" t="n">
-        <v>0.4165482630488806</v>
+        <v>-0.01196274517880961</v>
       </c>
       <c r="E41" t="n">
-        <v>0.322915851208086</v>
+        <v>0.3906398463107298</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.9017143829519831</v>
+        <v>-0.7905971041557257</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>LSC-43</t>
+          <t>LSC-55</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6876157413835747</v>
+        <v>0.4399876093935412</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.686155877600648</v>
+        <v>-0.04321452658019993</v>
       </c>
       <c r="D42" t="n">
-        <v>0.4641712500222333</v>
+        <v>0.1154642056685933</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4009832198433276</v>
+        <v>1.123316946830629</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3031174559420027</v>
+        <v>0.4603838715405493</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>LSC-45</t>
+          <t>LSC-56</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.112180458748165</v>
+        <v>0.05125691827214916</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.1711369698066595</v>
+        <v>-0.65371338763225</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3713957032374798</v>
+        <v>0.5552927134322064</v>
       </c>
       <c r="E43" t="n">
-        <v>1.180831588807663</v>
+        <v>0.6948483090325821</v>
       </c>
       <c r="F43" t="n">
-        <v>0.6524191895912486</v>
+        <v>0.009473116478452961</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>LSC-47</t>
+          <t>LSC-57</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.102831465932208</v>
+        <v>-0.948336287468573</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.4150932945511806</v>
+        <v>0.6971777091637777</v>
       </c>
       <c r="D44" t="n">
-        <v>0.5291116868040756</v>
+        <v>1.114327078440163</v>
       </c>
       <c r="E44" t="n">
-        <v>1.301774952110327</v>
+        <v>0.7644206284618633</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1469001913275854</v>
+        <v>0.4197738442632417</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>LSC-48</t>
+          <t>LSC-58</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8763111713233926</v>
+        <v>0.939784212263902</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.9978778481075371</v>
+        <v>0.892017771201667</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1308103412087719</v>
+        <v>0.1730118608900008</v>
       </c>
       <c r="E45" t="n">
-        <v>1.283758463776653</v>
+        <v>0.1764802133735906</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1394844735155864</v>
+        <v>-0.7399929871423291</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>LSC-53</t>
+          <t>LSC-59</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.9162954131048767</v>
+        <v>0.2733887417700874</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1541381298527027</v>
+        <v>1.840239406452726</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.01638798216340526</v>
+        <v>0.6827196642796078</v>
       </c>
       <c r="E46" t="n">
-        <v>0.312657028916163</v>
+        <v>0.1693855376481929</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.8314497522111602</v>
+        <v>-0.3757237961324835</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>LSC-55</t>
+          <t>LSC-60</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.2630510240189848</v>
+        <v>1.106383079887356</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.04915880743439899</v>
+        <v>-0.4848520005327476</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1178222538524043</v>
+        <v>0.1935645948976451</v>
       </c>
       <c r="E47" t="n">
-        <v>1.060228334719891</v>
+        <v>0.5417280102215581</v>
       </c>
       <c r="F47" t="n">
-        <v>0.410702723143749</v>
+        <v>0.07354448625200374</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>LSC-56</t>
+          <t>LSC-62</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.06716597837569646</v>
+        <v>0.6065864770169949</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.686155877600648</v>
+        <v>-0.3030012759640507</v>
       </c>
       <c r="D48" t="n">
-        <v>0.5810640362295504</v>
+        <v>-0.3901330509194855</v>
       </c>
       <c r="E48" t="n">
-        <v>0.6230495845892515</v>
+        <v>-0.03188161926948377</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.03702583663933803</v>
+        <v>-0.2768626411358564</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>LSC-57</t>
+          <t>SCR-08</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.9162954131048767</v>
+        <v>-0.2819408169747583</v>
       </c>
       <c r="C49" t="n">
-        <v>0.723369554256586</v>
+        <v>0.2685295726804224</v>
       </c>
       <c r="D49" t="n">
-        <v>1.169857329718259</v>
+        <v>-0.1352791492246813</v>
       </c>
       <c r="E49" t="n">
-        <v>0.6940362029053364</v>
+        <v>0.4894363180869628</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3703792914635335</v>
+        <v>-0.4451869175637931</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>LSC-58</t>
+          <t>DR-144</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6876157413835747</v>
+        <v>-0.6151385522216656</v>
       </c>
       <c r="C50" t="n">
-        <v>0.9266664915436877</v>
+        <v>-0.5238200129403245</v>
       </c>
       <c r="D50" t="n">
-        <v>0.1784333281821246</v>
+        <v>-0.5504443761791205</v>
       </c>
       <c r="E50" t="n">
-        <v>0.09414385806414712</v>
+        <v>-2.374664598118514</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.7812027617032876</v>
+        <v>-0.5094111360945767</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>LSC-59</t>
+          <t>DR-145</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.1215294515641213</v>
+        <v>-0.2264078611002737</v>
       </c>
       <c r="C51" t="n">
-        <v>1.916044919674248</v>
+        <v>0.5802736719410447</v>
       </c>
       <c r="D51" t="n">
-        <v>0.7152742722453584</v>
+        <v>-0.8381826522861567</v>
       </c>
       <c r="E51" t="n">
-        <v>0.08690495842810542</v>
+        <v>0.06598323331084587</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.4195043137660051</v>
+        <v>-0.3131947503985629</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>LSC-60</t>
+          <t>SCR-09</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8291373138384384</v>
+        <v>1.439580815134263</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.5099651986184949</v>
+        <v>0.2035828853344608</v>
       </c>
       <c r="D52" t="n">
-        <v>0.2000801404427377</v>
+        <v>-0.1352791492246813</v>
       </c>
       <c r="E52" t="n">
-        <v>0.4668165842047864</v>
+        <v>0.4707387232388957</v>
       </c>
       <c r="F52" t="n">
-        <v>0.02659336469927494</v>
+        <v>-0.6863612450000949</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>LSC-62</t>
+          <t>DR-159</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4045725964738481</v>
+        <v>-0.948336287468573</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.3202213904838663</v>
+        <v>1.047889820831977</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4146893277587075</v>
+        <v>0.320991545745048</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.1184536520779219</v>
+        <v>-2.34094985174638</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.3213408478290776</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>SCR-08</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>-0.3502091232854233</v>
-      </c>
-      <c r="C54" t="n">
-        <v>0.2761162922249633</v>
-      </c>
-      <c r="D54" t="n">
-        <v>-0.1462688557270898</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0.4134618819164155</v>
-      </c>
-      <c r="F54" t="n">
-        <v>-0.4884772157589837</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>DR-144</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>-0.6332522681951499</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-0.5506245860759142</v>
-      </c>
-      <c r="D55" t="n">
-        <v>-0.5835344633914992</v>
-      </c>
-      <c r="E55" t="n">
-        <v>-2.508861827070899</v>
-      </c>
-      <c r="F55" t="n">
-        <v>-0.5522481871611229</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>DR-145</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>-0.3030352658004687</v>
-      </c>
-      <c r="C56" t="n">
-        <v>0.6013913918843256</v>
-      </c>
-      <c r="D56" t="n">
-        <v>-0.886589835040099</v>
-      </c>
-      <c r="E56" t="n">
-        <v>-0.01859935666749868</v>
-      </c>
-      <c r="F56" t="n">
-        <v>-0.3574165518823844</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>SCR-09</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>1.112180458748165</v>
-      </c>
-      <c r="C57" t="n">
-        <v>0.2083506464625976</v>
-      </c>
-      <c r="D57" t="n">
-        <v>-0.1462688557270898</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0.3943841935513224</v>
-      </c>
-      <c r="F57" t="n">
-        <v>-0.7279495128099593</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>DR-156</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>-1.05781698555974</v>
-      </c>
-      <c r="C58" t="n">
-        <v>0.5065194878170112</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0.2303856776075978</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0.2409610723729339</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-0.9455531650510192</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>DR-157</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>-0.6804261256801044</v>
-      </c>
-      <c r="C59" t="n">
-        <v>-0.06271193658687212</v>
-      </c>
-      <c r="D59" t="n">
-        <v>-0.5445702013223935</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0.2785752074000461</v>
-      </c>
-      <c r="F59" t="n">
-        <v>-0.2321015219457077</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>DR-159</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>-0.9162954131048767</v>
-      </c>
-      <c r="C60" t="n">
-        <v>1.089304041373368</v>
-      </c>
-      <c r="D60" t="n">
-        <v>0.3342903764585473</v>
-      </c>
-      <c r="E60" t="n">
-        <v>-2.474461711450562</v>
-      </c>
-      <c r="F60" t="n">
-        <v>-0.6325187280595805</v>
+        <v>-0.5902521935051245</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_standardized_matrix.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_standardized_matrix.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1625449618446163</v>
+        <v>0.02737043202415234</v>
       </c>
       <c r="C2" t="n">
-        <v>1.346644582623407</v>
+        <v>1.401026011880257</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.923367007889838</v>
+        <v>-2.029541522400534</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.6173405082582101</v>
+        <v>-0.7158140251878977</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6769844169493342</v>
+        <v>-0.7186388594902738</v>
       </c>
     </row>
     <row r="3">
@@ -489,19 +489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.7817374198451194</v>
+        <v>-0.7747738406500133</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.2553737052436774</v>
+        <v>-0.2705265835914633</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4881537823405614</v>
+        <v>0.5103511161782069</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.9047558306178681</v>
+        <v>-1.009072061629796</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1702984827450448</v>
+        <v>0.1226645429019804</v>
       </c>
     </row>
     <row r="4">
@@ -511,19 +511,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6065864770169949</v>
+        <v>0.4045725964738481</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.727498618418839</v>
+        <v>-1.806547887538452</v>
       </c>
       <c r="D4" t="n">
-        <v>1.406175901348729</v>
+        <v>1.477242063818982</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7469044406579175</v>
+        <v>-0.8480117942465809</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9766332473290535</v>
+        <v>-1.016172989604608</v>
       </c>
     </row>
     <row r="5">
@@ -533,19 +533,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.6151385522216656</v>
+        <v>-0.6332522681951499</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8400604213248978</v>
+        <v>0.8724539749337953</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4147963317286595</v>
+        <v>-0.440665502471444</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6293313233378477</v>
+        <v>0.5562007387424492</v>
       </c>
       <c r="F5" t="n">
-        <v>2.067585269942616</v>
+        <v>2.00656168039755</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.161916035761841</v>
+        <v>0.8763111713233926</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.6926814000398291</v>
+        <v>-0.7268152650580697</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.164052976835385</v>
+        <v>-0.1765743928919499</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.60974710789045</v>
+        <v>-2.748723204855355</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3483940334940475</v>
+        <v>-0.392367424419386</v>
       </c>
     </row>
     <row r="7">
@@ -577,19 +577,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.1153419493513044</v>
+        <v>-0.2086875508305598</v>
       </c>
       <c r="C7" t="n">
-        <v>1.060879158301172</v>
+        <v>1.102857170525843</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2017856885007046</v>
+        <v>0.2087388653469847</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3169659006343107</v>
+        <v>0.2374854045621987</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4164379194144966</v>
+        <v>0.3670669091100285</v>
       </c>
     </row>
     <row r="8">
@@ -599,19 +599,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.439580815134263</v>
+        <v>1.112180458748165</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.9914361618312568</v>
+        <v>-1.038537235564956</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.114959470255782</v>
+        <v>-1.178100240149704</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.687654109804711</v>
+        <v>-1.807885465880997</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1396830659236304</v>
+        <v>-0.1851293848025029</v>
       </c>
     </row>
     <row r="9">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1.059402199217542</v>
+        <v>-1.010643128074786</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.147308211461569</v>
+        <v>-1.201174785394639</v>
       </c>
       <c r="D9" t="n">
-        <v>2.647561035410515</v>
+        <v>2.784709524360085</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5374837171827732</v>
+        <v>0.4624860111775051</v>
       </c>
       <c r="F9" t="n">
-        <v>5.64663917589164</v>
+        <v>5.560357265681184</v>
       </c>
     </row>
     <row r="10">
@@ -643,19 +643,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-1.39259993446445</v>
+        <v>-1.293686272984512</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.978625809489895</v>
+        <v>-2.068575051152938</v>
       </c>
       <c r="D10" t="n">
-        <v>2.758545799051801</v>
+        <v>2.901602310567402</v>
       </c>
       <c r="E10" t="n">
-        <v>0.498624289483356</v>
+        <v>0.4228366307240621</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3773355865696147</v>
+        <v>-0.42110472937594</v>
       </c>
     </row>
     <row r="11">
@@ -665,19 +665,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.939784212263902</v>
+        <v>0.6876157413835747</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6062523468794293</v>
+        <v>0.6284976501892717</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2428911565159946</v>
+        <v>0.2520324898682124</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3081004107896048</v>
+        <v>0.228439692863152</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.055759724886506</v>
+        <v>-1.094741050888993</v>
       </c>
     </row>
     <row r="12">
@@ -687,921 +687,1075 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.7817374198451194</v>
+        <v>-0.7747738406500133</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7231563841021623</v>
+        <v>0.7504758125615323</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4353490657363053</v>
+        <v>-0.4623123147320586</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4236680352596511</v>
+        <v>0.3463566304505318</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3598364967265706</v>
+        <v>-0.4037291351924258</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>DR-143</t>
+          <t>DR-141</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.7817374198451194</v>
+        <v>1.819788321022482</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6971777091637777</v>
+        <v>0.09992561324281021</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.7600822630571049</v>
+        <v>-0.7134153369551852</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.363790299088561</v>
+        <v>-0.001629463595240271</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1405268662293444</v>
+        <v>0.3116832204964367</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>SCR-11</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.7817374198451194</v>
+        <v>-0.7747738406500133</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.212254898807531</v>
+        <v>0.723369554256586</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.05306821319409968</v>
+        <v>-0.8043319484497656</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4120772378185887</v>
+        <v>-2.497766470167082</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.436209523752609</v>
+        <v>-0.1859672301884925</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>SCR-14</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.994910373879109</v>
+        <v>-0.7747738406500133</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2425508977420378</v>
+        <v>-1.268940431157005</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1236852992716513</v>
+        <v>-0.05968160668463292</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5153994939182676</v>
+        <v>0.334530209818342</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2543135791649461</v>
+        <v>-0.4795631777668459</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SCR-17</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05125691827214916</v>
+        <v>1.58391903359771</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6971777091637777</v>
+        <v>0.249010033920017</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3490275829041954</v>
+        <v>0.1264809787566499</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.381333988357456</v>
+        <v>0.4399528494179898</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5350117277310629</v>
+        <v>-0.2989509204934456</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>SCR-18</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6065864770169949</v>
+        <v>-0.06716597837569646</v>
       </c>
       <c r="C17" t="n">
-        <v>1.086857833239556</v>
+        <v>0.723369554256586</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2503744596674964</v>
+        <v>-0.3713957032374798</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5179632245454837</v>
+        <v>-2.515666795816752</v>
       </c>
       <c r="F17" t="n">
-        <v>0.07204052477201671</v>
+        <v>0.4848039110102405</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>SCR-19</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.2819408169747583</v>
+        <v>0.4045725964738481</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2815189101496147</v>
+        <v>1.129963428830789</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1565696736838833</v>
+        <v>-0.2674910043865303</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.629228038395292</v>
+        <v>0.4425686967692404</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2117590226726129</v>
+        <v>0.02510001706929636</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>SCR-20</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.328921697644572</v>
+        <v>-0.3502091232854233</v>
       </c>
       <c r="C19" t="n">
-        <v>1.034900483362785</v>
+        <v>0.2896694213774364</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3086599053404602</v>
+        <v>0.161115878373632</v>
       </c>
       <c r="E19" t="n">
-        <v>0.02224072301892923</v>
+        <v>-2.768600152893506</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7715186592284551</v>
+        <v>0.1638324849419587</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>LSC-14</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.717245594506686</v>
+        <v>0.1687033090490758</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5672843344718523</v>
+        <v>1.075750912220895</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8875092139045062</v>
+        <v>0.3213022891021782</v>
       </c>
       <c r="E20" t="n">
-        <v>0.01833772542713712</v>
+        <v>-0.06323108531693668</v>
       </c>
       <c r="F20" t="n">
-        <v>0.285385411549008</v>
+        <v>0.719641751157704</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>LSC-15</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.717245594506686</v>
+        <v>1.348049746172937</v>
       </c>
       <c r="C21" t="n">
-        <v>-2.96581545714853</v>
+        <v>0.5878382627318524</v>
       </c>
       <c r="D21" t="n">
-        <v>0.838920442737713</v>
+        <v>-0.9385421844655737</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5141166153398881</v>
+        <v>-0.06721342488258492</v>
       </c>
       <c r="F21" t="n">
-        <v>0.159965764456089</v>
+        <v>0.236939273111423</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>LSC-16</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-1.059402199217542</v>
+        <v>1.348049746172937</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8270710838557032</v>
+        <v>-3.098612866740916</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.340806489301136</v>
+        <v>0.8797900454260266</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.06204448340379655</v>
+        <v>0.4386438918794693</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6491256291177548</v>
+        <v>0.1124047453118309</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>LSC-17</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.6151385522216656</v>
+        <v>-1.010643128074786</v>
       </c>
       <c r="C23" t="n">
-        <v>0.294508247618807</v>
+        <v>0.8589008457813198</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4024646913240733</v>
+        <v>-0.3627369783332327</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5907669290014725</v>
+        <v>-0.1492296811249172</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7568467638217257</v>
+        <v>-0.690976678419836</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>LSC-18</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.948336287468573</v>
+        <v>-0.6332522681951499</v>
       </c>
       <c r="C24" t="n">
-        <v>0.138636197988497</v>
+        <v>0.3032225505299095</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.101956812700258</v>
+        <v>-0.4276774151150765</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7354648815165094</v>
+        <v>0.5168523892292507</v>
       </c>
       <c r="F24" t="n">
-        <v>0.03333337641270224</v>
+        <v>0.7050733991590065</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>LSC-19</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.4485396845982119</v>
+        <v>-0.9162954131048767</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7231563841021623</v>
+        <v>0.1405850007002296</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.932725228721326</v>
+        <v>-4.32410362202565</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5919759772655775</v>
+        <v>0.6644918298942235</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.3884235386270447</v>
+        <v>-0.01333396480775942</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>LSC-22</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-1.337066978589965</v>
+        <v>-0.4917306957402865</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1776042103960739</v>
+        <v>0.7504758125615323</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.800050603843965</v>
+        <v>-0.9861651714389249</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4249236513755772</v>
+        <v>0.5180860155960846</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4203848272351433</v>
+        <v>-0.4321144308520855</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>LSC-23</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.337066978589965</v>
+        <v>-1.246512415499558</v>
       </c>
       <c r="C27" t="n">
-        <v>-3.329516906285923</v>
+        <v>0.181244388157649</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9540157531805281</v>
+        <v>-1.899660648836848</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4433212471191591</v>
+        <v>0.3476377713224181</v>
       </c>
       <c r="F27" t="n">
-        <v>0.09796945472235387</v>
+        <v>0.3709859625686035</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>LSC-24</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.059402199217542</v>
+        <v>-1.246512415499558</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3854336099031554</v>
+        <v>-3.478100483010172</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2757755309282282</v>
+        <v>1.001012194085467</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5960334726976462</v>
+        <v>0.366409362059892</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0885796460871459</v>
+        <v>0.05084595977093423</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>LSC-25</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.059402199217542</v>
+        <v>-1.010643128074786</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5542949970026601</v>
+        <v>0.3980944545972238</v>
       </c>
       <c r="D29" t="n">
-        <v>0.05380600364565596</v>
+        <v>0.286667389485196</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4439370495412633</v>
+        <v>0.5222259937068947</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.2300491029169095</v>
+        <v>0.04152241747418529</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>LSC-26</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.170468110966511</v>
+        <v>-1.010643128074786</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6062523468794293</v>
+        <v>0.5742851335793793</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.06951040040021569</v>
+        <v>0.05288181707056053</v>
       </c>
       <c r="E30" t="n">
-        <v>0.426663415580869</v>
+        <v>0.3670376828037543</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.9238554615919605</v>
+        <v>-0.2748576850084588</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>LSC-27</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5040726404726965</v>
+        <v>-1.104990843044694</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.5108306754711323</v>
+        <v>0.6284976501892717</v>
       </c>
       <c r="D31" t="n">
-        <v>0.320991545745048</v>
+        <v>-0.076999056493124</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4910523211544791</v>
+        <v>0.3494129022741261</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.6041996719497911</v>
+        <v>-0.9637676705224428</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>SCR-06</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.939784212263902</v>
+        <v>-0.538904553225241</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5283163220642755</v>
+        <v>-0.5370714569234412</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.06128930679715769</v>
+        <v>0.3342903764585473</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.04299913330944569</v>
+        <v>0.415110735855632</v>
       </c>
       <c r="F32" t="n">
-        <v>0.02840842303729856</v>
+        <v>-0.6463677754964203</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>LSC-37</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.272575153251532</v>
+        <v>0.6876157413835747</v>
       </c>
       <c r="C33" t="n">
-        <v>-1.017414836769644</v>
+        <v>0.547178875274433</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4073130285771593</v>
+        <v>-0.06834033158887846</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7375188350154369</v>
+        <v>-0.1297971681810568</v>
       </c>
       <c r="F33" t="n">
-        <v>1.208238844380852</v>
+        <v>-0.01822416149748947</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>LSC-38</t>
+          <t>LSC-30</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3930067287237273</v>
+        <v>-0.538904553225241</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3724442724339632</v>
+        <v>0.1134787423952833</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2264489693098786</v>
+        <v>0.2650205772245814</v>
       </c>
       <c r="E34" t="n">
-        <v>0.4742704592779454</v>
+        <v>0.870773913517998</v>
       </c>
       <c r="F34" t="n">
-        <v>0.736413572834494</v>
+        <v>2.509684649430614</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>LSC-39</t>
+          <t>LSC-32</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.28153402271548</v>
+        <v>3.235004045571116</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4893483096566962</v>
+        <v>0.9673258790011071</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1065053216139775</v>
+        <v>0.2996554768415636</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3600084368510182</v>
+        <v>0.4938301224612287</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.9220493852222107</v>
+        <v>0.4843712926379504</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>LSC-40</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7731853446404484</v>
+        <v>1.819788321022482</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1471292263337407</v>
+        <v>-1.065643493869905</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2346700629129366</v>
+        <v>0.4252069879531277</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3506971665703607</v>
+        <v>0.6665875371275516</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.6987947004720406</v>
+        <v>1.153279887599046</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>LSC-41</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.948336287468573</v>
+        <v>-0.444556838255332</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.315990613433243</v>
+        <v>0.3845413254447507</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9334630191728823</v>
+        <v>0.2347150400597213</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4059557840906765</v>
+        <v>0.3979877243844726</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9547265174248813</v>
+        <v>0.6847844105514359</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>LSC-42</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7731853446404484</v>
+        <v>-1.199338558014603</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.8485534496701391</v>
+        <v>0.5065194878170112</v>
       </c>
       <c r="D38" t="n">
-        <v>0.3990919349740998</v>
+        <v>-0.1159633185622297</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4006942773907377</v>
+        <v>0.2814029297336496</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.8613611351946513</v>
+        <v>-0.9619743401065938</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>LSC-43</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.939784212263902</v>
+        <v>0.5460941689287114</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.65371338763225</v>
+        <v>-0.1575838406541864</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4443079497909211</v>
+        <v>0.2433737649639669</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4772062741097559</v>
+        <v>0.2719023755639297</v>
       </c>
       <c r="F39" t="n">
-        <v>0.352033950572811</v>
+        <v>-0.7402952221306757</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>LSC-45</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.439580815134263</v>
+        <v>-0.9162954131048767</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.160118563802933</v>
+        <v>-0.3337745196363395</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3490275829041954</v>
+        <v>0.9793653818248526</v>
       </c>
       <c r="E40" t="n">
-        <v>1.24151736708792</v>
+        <v>0.3282843162950626</v>
       </c>
       <c r="F40" t="n">
-        <v>0.703818318629625</v>
+        <v>-0.9944208612301106</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>LSC-53</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.948336287468573</v>
+        <v>0.5460941689287114</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1516255354576893</v>
+        <v>-0.8894528148877496</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.01196274517880961</v>
+        <v>0.4165482630488806</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3906398463107298</v>
+        <v>0.322915851208086</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.7905971041557257</v>
+        <v>-0.9017143829519831</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>LSC-55</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4399876093935412</v>
+        <v>0.6876157413835747</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.04321452658019993</v>
+        <v>-0.686155877600648</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1154642056685933</v>
+        <v>0.4641712500222333</v>
       </c>
       <c r="E42" t="n">
-        <v>1.123316946830629</v>
+        <v>0.4009832198433276</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4603838715405493</v>
+        <v>0.3031174559420027</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>LSC-56</t>
+          <t>LSC-45</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.05125691827214916</v>
+        <v>1.112180458748165</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.65371338763225</v>
+        <v>-0.1711369698066595</v>
       </c>
       <c r="D43" t="n">
-        <v>0.5552927134322064</v>
+        <v>-0.3713957032374798</v>
       </c>
       <c r="E43" t="n">
-        <v>0.6948483090325821</v>
+        <v>1.180831588807663</v>
       </c>
       <c r="F43" t="n">
-        <v>0.009473116478452961</v>
+        <v>0.6524191895912486</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>LSC-57</t>
+          <t>LSC-47</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.948336287468573</v>
+        <v>2.102831465932208</v>
       </c>
       <c r="C44" t="n">
-        <v>0.6971777091637777</v>
+        <v>-0.4150932945511806</v>
       </c>
       <c r="D44" t="n">
-        <v>1.114327078440163</v>
+        <v>0.5291116868040756</v>
       </c>
       <c r="E44" t="n">
-        <v>0.7644206284618633</v>
+        <v>1.301774952110327</v>
       </c>
       <c r="F44" t="n">
-        <v>0.4197738442632417</v>
+        <v>0.1469001913275854</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>LSC-58</t>
+          <t>LSC-48</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.939784212263902</v>
+        <v>0.8763111713233926</v>
       </c>
       <c r="C45" t="n">
-        <v>0.892017771201667</v>
+        <v>-0.9978778481075371</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1730118608900008</v>
+        <v>0.1308103412087719</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1764802133735906</v>
+        <v>1.283758463776653</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.7399929871423291</v>
+        <v>0.1394844735155864</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>LSC-59</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.2733887417700874</v>
+        <v>-0.9162954131048767</v>
       </c>
       <c r="C46" t="n">
-        <v>1.840239406452726</v>
+        <v>0.1541381298527027</v>
       </c>
       <c r="D46" t="n">
-        <v>0.6827196642796078</v>
+        <v>-0.01638798216340526</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1693855376481929</v>
+        <v>0.312657028916163</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.3757237961324835</v>
+        <v>-0.8314497522111602</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>LSC-60</t>
+          <t>LSC-55</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.106383079887356</v>
+        <v>0.2630510240189848</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.4848520005327476</v>
+        <v>-0.04915880743439899</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1935645948976451</v>
+        <v>0.1178222538524043</v>
       </c>
       <c r="E47" t="n">
-        <v>0.5417280102215581</v>
+        <v>1.060228334719891</v>
       </c>
       <c r="F47" t="n">
-        <v>0.07354448625200374</v>
+        <v>0.410702723143749</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>LSC-62</t>
+          <t>LSC-56</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6065864770169949</v>
+        <v>-0.06716597837569646</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.3030012759640507</v>
+        <v>-0.686155877600648</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3901330509194855</v>
+        <v>0.5810640362295504</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.03188161926948377</v>
+        <v>0.6230495845892515</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.2768626411358564</v>
+        <v>-0.03702583663933803</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>SCR-08</t>
+          <t>LSC-57</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.2819408169747583</v>
+        <v>-0.9162954131048767</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2685295726804224</v>
+        <v>0.723369554256586</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.1352791492246813</v>
+        <v>1.169857329718259</v>
       </c>
       <c r="E49" t="n">
-        <v>0.4894363180869628</v>
+        <v>0.6940362029053364</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.4451869175637931</v>
+        <v>0.3703792914635335</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>DR-144</t>
+          <t>LSC-58</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.6151385522216656</v>
+        <v>0.6876157413835747</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.5238200129403245</v>
+        <v>0.9266664915436877</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5504443761791205</v>
+        <v>0.1784333281821246</v>
       </c>
       <c r="E50" t="n">
-        <v>-2.374664598118514</v>
+        <v>0.09414385806414712</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.5094111360945767</v>
+        <v>-0.7812027617032876</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>DR-145</t>
+          <t>LSC-59</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.2264078611002737</v>
+        <v>0.1215294515641213</v>
       </c>
       <c r="C51" t="n">
-        <v>0.5802736719410447</v>
+        <v>1.916044919674248</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.8381826522861567</v>
+        <v>0.7152742722453584</v>
       </c>
       <c r="E51" t="n">
-        <v>0.06598323331084587</v>
+        <v>0.08690495842810542</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.3131947503985629</v>
+        <v>-0.4195043137660051</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>SCR-09</t>
+          <t>LSC-60</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.439580815134263</v>
+        <v>0.8291373138384384</v>
       </c>
       <c r="C52" t="n">
-        <v>0.2035828853344608</v>
+        <v>-0.5099651986184949</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.1352791492246813</v>
+        <v>0.2000801404427377</v>
       </c>
       <c r="E52" t="n">
-        <v>0.4707387232388957</v>
+        <v>0.4668165842047864</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.6863612450000949</v>
+        <v>0.02659336469927494</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
+          <t>LSC-62</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0.4045725964738481</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.3202213904838663</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-0.4146893277587075</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-0.1184536520779219</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-0.3213408478290776</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>SCR-08</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>-0.3502091232854233</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.2761162922249633</v>
+      </c>
+      <c r="D54" t="n">
+        <v>-0.1462688557270898</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.4134618819164155</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-0.4884772157589837</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>DR-144</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>-0.6332522681951499</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.5506245860759142</v>
+      </c>
+      <c r="D55" t="n">
+        <v>-0.5835344633914992</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-2.508861827070899</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-0.5522481871611229</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>DR-145</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>-0.3030352658004687</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.6013913918843256</v>
+      </c>
+      <c r="D56" t="n">
+        <v>-0.886589835040099</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-0.01859935666749868</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-0.3574165518823844</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>SCR-09</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1.112180458748165</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.2083506464625976</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-0.1462688557270898</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.3943841935513224</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-0.7279495128099593</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>DR-156</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>-1.05781698555974</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.5065194878170112</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.2303856776075978</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.2409610723729339</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-0.9455531650510192</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>DR-157</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>-0.6804261256801044</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.06271193658687212</v>
+      </c>
+      <c r="D59" t="n">
+        <v>-0.5445702013223935</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.2785752074000461</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-0.2321015219457077</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
           <t>DR-159</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>-0.948336287468573</v>
-      </c>
-      <c r="C53" t="n">
-        <v>1.047889820831977</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0.320991545745048</v>
-      </c>
-      <c r="E53" t="n">
-        <v>-2.34094985174638</v>
-      </c>
-      <c r="F53" t="n">
-        <v>-0.5902521935051245</v>
+      <c r="B60" t="n">
+        <v>-0.9162954131048767</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1.089304041373368</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.3342903764585473</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-2.474461711450562</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-0.6325187280595805</v>
       </c>
     </row>
   </sheetData>
